--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_42.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3409389.433060262</v>
+        <v>3445741.068091149</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13279501.51514058</v>
+        <v>13275569.19337385</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13279501.51514058</v>
+        <v>13275569.19337385</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>987.0883260129401</v>
+        <v>603.5370117056943</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>987.0883260129401</v>
+        <v>603.5370117056943</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24937188.80302019</v>
+        <v>24938106.35291966</v>
       </c>
     </row>
   </sheetData>
@@ -666,13 +666,13 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708013072</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>1.415908396047664</v>
+        <v>5.146009903586449</v>
       </c>
       <c r="H2" t="n">
-        <v>3.769060713577687</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.41253966161941</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,25 +778,25 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.7989632036872</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>133.5184388018132</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
-        <v>62.44885845517734</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>373</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>373</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
-        <v>99.03770148143687</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>193.2512723758775</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N4" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O4" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P4" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.343301935257443</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>3.769060713577687</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I5" t="n">
-        <v>1.953406460791434</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.41253966161941</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>132.0068113193051</v>
       </c>
       <c r="R6" t="n">
-        <v>133.5184388018132</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>323.1609391857897</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T6" t="n">
-        <v>4.464774651476091</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N7" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O7" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P7" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>5.296708396048877</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>3.769060713577687</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.41253966161941</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1213,19 +1213,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>185.6283849028919</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1255,25 +1255,25 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>133.5184388018132</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S9" t="n">
-        <v>62.44885845517734</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T9" t="n">
-        <v>4.464774651476091</v>
+        <v>129.900647009937</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N10" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O10" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P10" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>142.3350019731772</v>
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63.55655664632661</v>
+        <v>158.5198244189524</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,19 +1489,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1510,10 +1510,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>272.4545553273608</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,28 +1553,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N13" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O13" t="n">
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1681,16 +1681,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>135.0631802181451</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>200.5295027796757</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>18.63624233787687</v>
@@ -1726,19 +1726,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V15" t="n">
         <v>93.51066719152016</v>
@@ -1796,13 +1796,13 @@
         <v>102.3923982877958</v>
       </c>
       <c r="N16" t="n">
-        <v>154.4197474548741</v>
+        <v>155.2579933044718</v>
       </c>
       <c r="O16" t="n">
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627038</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
@@ -1857,10 +1857,10 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H17" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
         <v>342.6720972219126</v>
@@ -1978,16 +1978,16 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V18" t="n">
-        <v>267.1024830734931</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273604</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2048,7 +2048,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2091,10 +2091,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H20" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S20" t="n">
         <v>142.3350019731772</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>237.1483725282997</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
         <v>40.09991244551929</v>
@@ -2167,13 +2167,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>192.2280582198497</v>
       </c>
       <c r="G21" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V21" t="n">
         <v>93.51066719152016</v>
@@ -2221,7 +2221,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>399.3913927661343</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2276,16 +2276,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q22" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>237.1483725282997</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -2461,7 +2461,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481073</v>
       </c>
     </row>
     <row r="25">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2522,7 +2522,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S25" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H26" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S26" t="n">
         <v>142.3350019731772</v>
@@ -2638,16 +2638,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H27" t="n">
-        <v>325.021973978874</v>
+        <v>177.6137898608469</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T27" t="n">
-        <v>254.9671660051475</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2750,16 +2750,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S28" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2799,10 +2799,10 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G29" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T29" t="n">
         <v>259.6218731858503</v>
@@ -2869,13 +2869,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
         <v>339.6362423378769</v>
@@ -2884,7 +2884,7 @@
         <v>324.9996113467254</v>
       </c>
       <c r="H30" t="n">
-        <v>177.6137898608471</v>
+        <v>177.6137898608467</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M31" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N31" t="n">
         <v>155.2579933044718</v>
@@ -2987,13 +2987,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S31" t="n">
         <v>30.56285675203577</v>
@@ -3036,10 +3036,10 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>84.35021607332619</v>
+        <v>84.350216073326</v>
       </c>
       <c r="G32" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H32" t="n">
         <v>72.84688483418068</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
         <v>40.09991244551929</v>
@@ -3115,13 +3115,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3154,13 +3154,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>252.7534963968766</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
@@ -3172,7 +3172,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481075</v>
       </c>
     </row>
     <row r="34">
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M34" t="n">
         <v>102.3923982877958</v>
@@ -3224,16 +3224,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S34" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4605873653143577</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
         <v>40.09991244551929</v>
@@ -3349,16 +3349,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3391,25 +3391,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T36" t="n">
-        <v>81.3753501231742</v>
+        <v>254.9671660051473</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V36" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>251.9832086481073</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,13 +3461,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>376.871685410242</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
         <v>30.56285675203577</v>
@@ -3513,7 +3513,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H38" t="n">
         <v>72.84688483418068</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S38" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T38" t="n">
         <v>259.6218731858503</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
         <v>40.09991244551929</v>
@@ -3589,13 +3589,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,25 +3625,25 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>353.9253867592579</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T39" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>272.4545553273606</v>
       </c>
       <c r="Y39" t="n">
         <v>78.39139276613435</v>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M40" t="n">
         <v>102.3923982877958</v>
@@ -3698,16 +3698,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q40" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T41" t="n">
         <v>259.6218731858503</v>
@@ -3820,19 +3820,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H42" t="n">
-        <v>177.6137898608469</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>180.333570877285</v>
+        <v>353.9253867592584</v>
       </c>
       <c r="S42" t="n">
         <v>131.8202263797056</v>
@@ -3871,7 +3871,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
@@ -3944,7 +3944,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090251361</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>40.09991244551929</v>
@@ -4063,7 +4063,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
         <v>3.99961134672543</v>
@@ -4072,7 +4072,7 @@
         <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4105,19 +4105,19 @@
         <v>131.8202263797057</v>
       </c>
       <c r="T45" t="n">
-        <v>81.3753501231742</v>
+        <v>254.9671660051471</v>
       </c>
       <c r="U45" t="n">
-        <v>382.1025822036415</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y45" t="n">
         <v>78.39139276613435</v>
@@ -4166,7 +4166,7 @@
         <v>102.3923982877958</v>
       </c>
       <c r="N46" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O46" t="n">
         <v>231.765039488851</v>
@@ -4178,7 +4178,7 @@
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>376.871685410242</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S46" t="n">
         <v>30.56285675203577</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.8416377852028</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C2" t="n">
-        <v>54.86731632763319</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D2" t="n">
-        <v>44.42372467121926</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E2" t="n">
-        <v>40.016361431958</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F2" t="n">
-        <v>35.0773425349751</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G2" t="n">
-        <v>33.64713203391685</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="I2" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.93969029977264</v>
+        <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>82.08427879223495</v>
+        <v>321.1580850251256</v>
       </c>
       <c r="L2" t="n">
-        <v>146.7742517570591</v>
+        <v>385.22</v>
       </c>
       <c r="M2" t="n">
-        <v>325.5257936111288</v>
+        <v>755.48</v>
       </c>
       <c r="N2" t="n">
-        <v>694.7957936111288</v>
+        <v>755.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1064.065793611129</v>
+        <v>1125.74</v>
       </c>
       <c r="P2" t="n">
-        <v>1122.73</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1405.724707412506</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T2" t="n">
-        <v>1218.994415731961</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U2" t="n">
-        <v>967.2891925799706</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V2" t="n">
-        <v>735.1164408963101</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W2" t="n">
-        <v>494.3351520266661</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X2" t="n">
-        <v>300.1110778239714</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y2" t="n">
-        <v>187.6692266292175</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241.454702729969</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="C3" t="n">
-        <v>241.454702729969</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="D3" t="n">
-        <v>241.454702729969</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="E3" t="n">
-        <v>241.454702729969</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="F3" t="n">
-        <v>241.454702729969</v>
+        <v>573.6316988789948</v>
       </c>
       <c r="G3" t="n">
-        <v>241.454702729969</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="H3" t="n">
-        <v>241.454702729969</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="I3" t="n">
-        <v>29.84</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="J3" t="n">
-        <v>174.5185557413367</v>
+        <v>177.6113405614803</v>
       </c>
       <c r="K3" t="n">
-        <v>399.1286311753428</v>
+        <v>401.8775591086939</v>
       </c>
       <c r="L3" t="n">
-        <v>714.3818833454036</v>
+        <v>720.3885386284223</v>
       </c>
       <c r="M3" t="n">
-        <v>856.0360750882628</v>
+        <v>861.5031803712816</v>
       </c>
       <c r="N3" t="n">
-        <v>1046.360878846775</v>
+        <v>1051.274153846774</v>
       </c>
       <c r="O3" t="n">
-        <v>1337.587921002191</v>
+        <v>1341.994549492757</v>
       </c>
       <c r="P3" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1345.738421006376</v>
+        <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>1210.871311105555</v>
+        <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>1147.791656100326</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>771.0239793326488</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>394.256302564972</v>
+        <v>1146.622528526128</v>
       </c>
       <c r="V3" t="n">
-        <v>294.2182202604903</v>
+        <v>1131.965288938734</v>
       </c>
       <c r="W3" t="n">
-        <v>261.5180759071281</v>
+        <v>936.7619835085549</v>
       </c>
       <c r="X3" t="n">
-        <v>241.454702729969</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="Y3" t="n">
-        <v>241.454702729969</v>
+        <v>916.6986103313957</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>909.5536253232013</v>
+        <v>862.9931484764093</v>
       </c>
       <c r="C4" t="n">
-        <v>909.5536253232013</v>
+        <v>988.9951542948451</v>
       </c>
       <c r="D4" t="n">
-        <v>909.5536253232013</v>
+        <v>1102.314298419845</v>
       </c>
       <c r="E4" t="n">
-        <v>1027.382529534614</v>
+        <v>1220.143202631258</v>
       </c>
       <c r="F4" t="n">
-        <v>1027.382529534614</v>
+        <v>1233.154887495874</v>
       </c>
       <c r="G4" t="n">
-        <v>1027.382529534614</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="H4" t="n">
-        <v>1027.382529534614</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I4" t="n">
-        <v>1027.382529534614</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J4" t="n">
-        <v>1249.633272693181</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K4" t="n">
-        <v>1381.361257449721</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
-        <v>1385.387095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1292.946305617309</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1148.742122945132</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>932.3861797621563</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>664.7258098826245</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.3053387456568</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.84</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>29.84</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U4" t="n">
-        <v>276.4012224743522</v>
+        <v>316.9048008472139</v>
       </c>
       <c r="V4" t="n">
-        <v>475.2226153602982</v>
+        <v>316.9048008472139</v>
       </c>
       <c r="W4" t="n">
-        <v>647.1135336199756</v>
+        <v>488.7957191068913</v>
       </c>
       <c r="X4" t="n">
-        <v>798.144324644169</v>
+        <v>639.8265101310848</v>
       </c>
       <c r="Y4" t="n">
-        <v>909.5536253232013</v>
+        <v>751.2358108101171</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.8416377852028</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>58.86731632763319</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>48.42372467121926</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>44.016361431958</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>39.07734253497633</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>35.70026987310013</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
-        <v>31.89313783918327</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>326.5557936111289</v>
+        <v>211.4278628071088</v>
       </c>
       <c r="K5" t="n">
-        <v>696.8157936111289</v>
+        <v>263.0661931588676</v>
       </c>
       <c r="L5" t="n">
-        <v>1067.075793611129</v>
+        <v>327.128108133742</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.075793611129</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.335793611129</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.335793611129</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.724707412506</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.994415731961</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>971.2891925799706</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>739.1164408963101</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>498.3351520266661</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>304.1110778239714</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.6692266292175</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>584.60161418237</v>
+        <v>1089.186506748585</v>
       </c>
       <c r="C6" t="n">
-        <v>584.60161418237</v>
+        <v>724.4391204399794</v>
       </c>
       <c r="D6" t="n">
-        <v>584.60161418237</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="E6" t="n">
-        <v>584.60161418237</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="F6" t="n">
-        <v>241.534702729969</v>
+        <v>29.92</v>
       </c>
       <c r="G6" t="n">
-        <v>241.534702729969</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
-        <v>241.534702729969</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.5985557413367</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K6" t="n">
-        <v>399.2086311753428</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L6" t="n">
-        <v>718.1819687139391</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M6" t="n">
-        <v>859.8361604567983</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N6" t="n">
-        <v>1050.16096421531</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1341.388006370727</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P6" t="n">
-        <v>1495.800085368536</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1495.800085368536</v>
+        <v>1359.445816914692</v>
       </c>
       <c r="R6" t="n">
-        <v>1360.932975467714</v>
+        <v>1224.443810882748</v>
       </c>
       <c r="S6" t="n">
-        <v>1034.507784370957</v>
+        <v>1161.323799483389</v>
       </c>
       <c r="T6" t="n">
-        <v>1029.997910985627</v>
+        <v>1156.805168712887</v>
       </c>
       <c r="U6" t="n">
-        <v>1029.800149078063</v>
+        <v>1156.6072638665</v>
       </c>
       <c r="V6" t="n">
-        <v>1015.142909490669</v>
+        <v>1141.950024279106</v>
       </c>
       <c r="W6" t="n">
-        <v>982.442765137307</v>
+        <v>1109.249879925744</v>
       </c>
       <c r="X6" t="n">
-        <v>962.3793919601478</v>
+        <v>1089.186506748585</v>
       </c>
       <c r="Y6" t="n">
-        <v>962.3793919601478</v>
+        <v>1089.186506748585</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1250.707100357225</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="C7" t="n">
-        <v>1376.709106175661</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="D7" t="n">
-        <v>1385.467095409585</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="E7" t="n">
-        <v>1385.467095409585</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="F7" t="n">
-        <v>1385.467095409585</v>
+        <v>700.1293446184156</v>
       </c>
       <c r="G7" t="n">
-        <v>1385.467095409585</v>
+        <v>853.7180055872682</v>
       </c>
       <c r="H7" t="n">
-        <v>1385.467095409585</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="I7" t="n">
-        <v>1385.467095409585</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J7" t="n">
-        <v>1385.467095409585</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K7" t="n">
-        <v>1385.467095409585</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L7" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M7" t="n">
-        <v>1293.026305617309</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N7" t="n">
-        <v>1148.822122945132</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O7" t="n">
-        <v>932.4661797621563</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P7" t="n">
-        <v>664.8058098826245</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.3853387456568</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.37478771712392</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T7" t="n">
-        <v>259.2361373677321</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U7" t="n">
-        <v>505.7973598420842</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V7" t="n">
-        <v>704.6187527280301</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="W7" t="n">
-        <v>876.5096709877075</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="X7" t="n">
-        <v>1027.540462011901</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="Y7" t="n">
-        <v>1138.949762690933</v>
+        <v>575.7683720264802</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.8416377852028</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C8" t="n">
-        <v>58.86731632763319</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D8" t="n">
-        <v>48.42372467121926</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E8" t="n">
-        <v>44.016361431958</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F8" t="n">
-        <v>39.07734253497633</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G8" t="n">
-        <v>33.72713203391686</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4795,22 +4795,22 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>30.01969029977264</v>
+        <v>29.92</v>
       </c>
       <c r="K8" t="n">
-        <v>326.5557936111288</v>
+        <v>400.18</v>
       </c>
       <c r="L8" t="n">
-        <v>696.8157936111288</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>1067.075793611129</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.075793611129</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1437.335793611129</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.724707412506</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.994415731961</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U8" t="n">
-        <v>971.2891925799706</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V8" t="n">
-        <v>739.1164408963101</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W8" t="n">
-        <v>498.3351520266661</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X8" t="n">
-        <v>304.1110778239714</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.6692266292175</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1225.724928051676</v>
+        <v>29.92</v>
       </c>
       <c r="C9" t="n">
-        <v>1225.724928051676</v>
+        <v>29.92</v>
       </c>
       <c r="D9" t="n">
-        <v>1038.221508957845</v>
+        <v>29.92</v>
       </c>
       <c r="E9" t="n">
-        <v>692.0880774205598</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>692.0880774205598</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
-        <v>363.2820282233719</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.5985557413367</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K9" t="n">
-        <v>399.2086311753428</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L9" t="n">
-        <v>718.1819687139391</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M9" t="n">
-        <v>859.8361604567983</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N9" t="n">
-        <v>1050.16096421531</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1341.388006370727</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P9" t="n">
-        <v>1495.800085368536</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1495.800085368536</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1360.932975467714</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S9" t="n">
-        <v>1297.853320462485</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T9" t="n">
-        <v>1293.343447077155</v>
+        <v>1163.45123817972</v>
       </c>
       <c r="U9" t="n">
-        <v>1293.145685169591</v>
+        <v>1163.253333333334</v>
       </c>
       <c r="V9" t="n">
-        <v>1278.488445582197</v>
+        <v>785.4755555555557</v>
       </c>
       <c r="W9" t="n">
-        <v>1245.788301228835</v>
+        <v>407.6977777777778</v>
       </c>
       <c r="X9" t="n">
-        <v>1225.724928051676</v>
+        <v>29.92</v>
       </c>
       <c r="Y9" t="n">
-        <v>1225.724928051676</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1098.49497497381</v>
+        <v>616.4320233791061</v>
       </c>
       <c r="C10" t="n">
-        <v>1224.496980792245</v>
+        <v>742.4340291975419</v>
       </c>
       <c r="D10" t="n">
-        <v>1337.816124917245</v>
+        <v>855.753173322542</v>
       </c>
       <c r="E10" t="n">
-        <v>1337.816124917245</v>
+        <v>855.753173322542</v>
       </c>
       <c r="F10" t="n">
-        <v>1337.816124917245</v>
+        <v>980.1141459144775</v>
       </c>
       <c r="G10" t="n">
-        <v>1337.816124917245</v>
+        <v>1133.70280688333</v>
       </c>
       <c r="H10" t="n">
-        <v>1337.816124917245</v>
+        <v>1133.70280688333</v>
       </c>
       <c r="I10" t="n">
-        <v>1337.816124917245</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J10" t="n">
-        <v>1337.816124917245</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K10" t="n">
-        <v>1381.441257449721</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L10" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M10" t="n">
-        <v>1293.026305617309</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N10" t="n">
-        <v>1148.822122945132</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O10" t="n">
-        <v>932.4661797621563</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P10" t="n">
-        <v>664.8058098826245</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.3853387456568</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7813496506081</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U10" t="n">
-        <v>465.3425721249604</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="V10" t="n">
-        <v>664.1639650109064</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="W10" t="n">
-        <v>836.0548832705838</v>
+        <v>242.2345940095882</v>
       </c>
       <c r="X10" t="n">
-        <v>987.0856742947773</v>
+        <v>393.2653850337817</v>
       </c>
       <c r="Y10" t="n">
-        <v>1098.49497497381</v>
+        <v>504.674685712814</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C11" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D11" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E11" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F11" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G11" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>733.5813277110226</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L11" t="n">
-        <v>949.6332762537361</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M11" t="n">
-        <v>1205.91497964478</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N11" t="n">
-        <v>1205.91497964478</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
-        <v>1367.045081027735</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P11" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
       </c>
       <c r="R11" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S11" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X11" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>816.937701241021</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C12" t="n">
-        <v>776.43273917484</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D12" t="n">
         <v>424.9805301872615</v>
       </c>
       <c r="E12" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F12" t="n">
-        <v>60.02261143999941</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R12" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S12" t="n">
-        <v>1928.880474452383</v>
+        <v>1525.215274341931</v>
       </c>
       <c r="T12" t="n">
-        <v>1846.683151095642</v>
+        <v>1443.01795098519</v>
       </c>
       <c r="U12" t="n">
-        <v>1766.721857646244</v>
+        <v>1038.814233293368</v>
       </c>
       <c r="V12" t="n">
-        <v>1672.26663826087</v>
+        <v>944.3590139079937</v>
       </c>
       <c r="W12" t="n">
-        <v>1559.768514109528</v>
+        <v>831.8608897566518</v>
       </c>
       <c r="X12" t="n">
-        <v>1284.561892566739</v>
+        <v>731.9995367815128</v>
       </c>
       <c r="Y12" t="n">
-        <v>881.1362433080176</v>
+        <v>652.8163117652155</v>
       </c>
     </row>
     <row r="13">
@@ -5202,19 +5202,19 @@
         <v>1505.227982468588</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R13" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5272,22 +5272,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>775.9368380887173</v>
+        <v>310.7478922784251</v>
       </c>
       <c r="L14" t="n">
-        <v>991.9887866314309</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M14" t="n">
-        <v>1634.498786631431</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N14" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O14" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P14" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264.3753454557946</v>
+        <v>668.0405455662464</v>
       </c>
       <c r="C15" t="n">
-        <v>127.9478906899915</v>
+        <v>627.5355835000653</v>
       </c>
       <c r="D15" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E15" t="n">
         <v>78.84709864997603</v>
@@ -5369,31 +5369,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q15" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R15" t="n">
-        <v>1658.367018159816</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S15" t="n">
-        <v>1200.972850099507</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1118.775526742765</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U15" t="n">
-        <v>1038.814233293368</v>
+        <v>1118.237009161395</v>
       </c>
       <c r="V15" t="n">
-        <v>944.3590139079937</v>
+        <v>1023.781789776021</v>
       </c>
       <c r="W15" t="n">
-        <v>831.8608897566518</v>
+        <v>911.2836656246792</v>
       </c>
       <c r="X15" t="n">
-        <v>731.9995367815128</v>
+        <v>811.4223126495402</v>
       </c>
       <c r="Y15" t="n">
-        <v>652.8163117652155</v>
+        <v>732.2390876332429</v>
       </c>
     </row>
     <row r="16">
@@ -5439,10 +5439,10 @@
         <v>1505.227982468588</v>
       </c>
       <c r="N16" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O16" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P16" t="n">
         <v>820.7766206439126</v>
@@ -5500,22 +5500,22 @@
         <v>125.9679517166617</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L17" t="n">
-        <v>991.9887866314309</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M17" t="n">
-        <v>1634.498786631431</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N17" t="n">
         <v>2238.277892278425</v>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>492.6952769985969</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C18" t="n">
-        <v>452.1903149324157</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D18" t="n">
         <v>424.9805301872615</v>
@@ -5621,16 +5621,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V18" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W18" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X18" t="n">
         <v>1284.561892566739</v>
       </c>
       <c r="Y18" t="n">
-        <v>881.1362433080177</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="19">
@@ -5670,25 +5670,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M19" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N19" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O19" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C20" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D20" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E20" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F20" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G20" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H20" t="n">
         <v>51.92</v>
@@ -5743,22 +5743,22 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L20" t="n">
-        <v>1376.091327711023</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M20" t="n">
-        <v>2018.601327711023</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N20" t="n">
-        <v>2238.277892278425</v>
+        <v>1310.98</v>
       </c>
       <c r="O20" t="n">
-        <v>2399.40799366138</v>
+        <v>1953.49</v>
       </c>
       <c r="P20" t="n">
         <v>2596</v>
@@ -5767,28 +5767,28 @@
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S20" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W20" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X20" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>168.4528527561725</v>
+        <v>343.7981213238219</v>
       </c>
       <c r="C21" t="n">
-        <v>127.9478906899915</v>
+        <v>303.2931592576408</v>
       </c>
       <c r="D21" t="n">
-        <v>100.7381059448373</v>
+        <v>276.0833745124866</v>
       </c>
       <c r="E21" t="n">
-        <v>78.84709864997603</v>
+        <v>254.1923672176254</v>
       </c>
       <c r="F21" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5852,7 +5852,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U21" t="n">
         <v>1766.721857646244</v>
@@ -5861,13 +5861,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W21" t="n">
-        <v>1235.526089867104</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X21" t="n">
-        <v>811.4223126495403</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y21" t="n">
-        <v>407.9966633908188</v>
+        <v>732.2390876332428</v>
       </c>
     </row>
     <row r="22">
@@ -5919,13 +5919,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5983,22 +5983,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K23" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L23" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M23" t="n">
-        <v>2060.956838088718</v>
+        <v>563.4049796447796</v>
       </c>
       <c r="N23" t="n">
-        <v>2238.277892278425</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O23" t="n">
-        <v>2399.40799366138</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
@@ -6038,10 +6038,10 @@
         <v>1141.180125483445</v>
       </c>
       <c r="C24" t="n">
-        <v>776.43273917484</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D24" t="n">
-        <v>424.9805301872616</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E24" t="n">
         <v>403.0895228924003</v>
@@ -6104,7 +6104,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>1380.723936118092</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="25">
@@ -6144,25 +6144,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L25" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M25" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N25" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O25" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q25" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R25" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D26" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H26" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
@@ -6223,16 +6223,16 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L26" t="n">
-        <v>1418.446838088717</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M26" t="n">
-        <v>2060.956838088718</v>
+        <v>1149.849898617045</v>
       </c>
       <c r="N26" t="n">
-        <v>2238.277892278425</v>
+        <v>1792.359898617045</v>
       </c>
       <c r="O26" t="n">
-        <v>2399.40799366138</v>
+        <v>1953.49</v>
       </c>
       <c r="P26" t="n">
         <v>2596</v>
@@ -6241,28 +6241,28 @@
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S26" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>492.6952769985969</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C27" t="n">
-        <v>452.1903149324157</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D27" t="n">
-        <v>424.9805301872615</v>
+        <v>1248.81064723976</v>
       </c>
       <c r="E27" t="n">
-        <v>403.0895228924003</v>
+        <v>902.6772157024741</v>
       </c>
       <c r="F27" t="n">
-        <v>384.2650356824237</v>
+        <v>559.6103042500731</v>
       </c>
       <c r="G27" t="n">
-        <v>380.2250242210849</v>
+        <v>231.32786854631</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6320,28 +6320,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R27" t="n">
-        <v>1737.789794027844</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S27" t="n">
-        <v>1280.395625967535</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T27" t="n">
-        <v>1022.853034043143</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U27" t="n">
-        <v>942.8917405937456</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V27" t="n">
-        <v>848.4365212083717</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W27" t="n">
-        <v>735.9383970570298</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X27" t="n">
-        <v>636.0770440818908</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y27" t="n">
-        <v>556.8938190655934</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="28">
@@ -6381,25 +6381,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N28" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O28" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P28" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R28" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G29" t="n">
         <v>125.5027119537179</v>
@@ -6454,25 +6454,25 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>1201.938527309012</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L29" t="n">
-        <v>1595.767892278425</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M29" t="n">
-        <v>2238.277892278425</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N29" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O29" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
@@ -6481,25 +6481,25 @@
         <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="30">
@@ -6512,19 +6512,19 @@
         <v>1316.525394051095</v>
       </c>
       <c r="C30" t="n">
-        <v>951.7780077424895</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D30" t="n">
-        <v>924.5682229973354</v>
+        <v>1248.810647239759</v>
       </c>
       <c r="E30" t="n">
-        <v>902.6772157024742</v>
+        <v>902.6772157024739</v>
       </c>
       <c r="F30" t="n">
-        <v>559.6103042500733</v>
+        <v>559.6103042500729</v>
       </c>
       <c r="G30" t="n">
-        <v>231.3278685463102</v>
+        <v>231.3278685463098</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6563,7 +6563,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U30" t="n">
         <v>1766.721857646244</v>
@@ -6578,7 +6578,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y30" t="n">
-        <v>1380.723936118092</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="31">
@@ -6618,7 +6618,7 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
         <v>1506.07469544798</v>
@@ -6633,7 +6633,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R31" t="n">
         <v>82.79157247680381</v>
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D32" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F32" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G32" t="n">
         <v>125.5027119537179</v>
@@ -6694,22 +6694,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K32" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L32" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M32" t="n">
-        <v>2060.956838088718</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N32" t="n">
-        <v>2060.956838088718</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O32" t="n">
-        <v>2222.086939471673</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P32" t="n">
-        <v>2418.678945810293</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6727,16 +6727,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W32" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1141.180125483445</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C33" t="n">
-        <v>1100.675163417264</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D33" t="n">
-        <v>749.2229544296858</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F33" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G33" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6800,19 +6800,19 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T33" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U33" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V33" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W33" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X33" t="n">
-        <v>1284.561892566739</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y33" t="n">
         <v>1205.378667550442</v>
@@ -6867,13 +6867,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q34" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R34" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6904,49 +6904,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D35" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H35" t="n">
-        <v>52.3852397629438</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L35" t="n">
-        <v>949.6332762537361</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M35" t="n">
-        <v>1592.143276253736</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N35" t="n">
-        <v>2234.653276253736</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O35" t="n">
-        <v>2395.783377636692</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P35" t="n">
-        <v>2592.375383975311</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
@@ -6964,16 +6964,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W35" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>816.937701241021</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C36" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D36" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E36" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F36" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7037,22 +7037,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1846.683151095641</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U36" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V36" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W36" t="n">
-        <v>1559.768514109528</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X36" t="n">
-        <v>1459.907161134389</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y36" t="n">
-        <v>1205.378667550442</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="37">
@@ -7092,22 +7092,22 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L37" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M37" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N37" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O37" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R37" t="n">
         <v>82.79157247680381</v>
@@ -7153,7 +7153,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G38" t="n">
         <v>125.5027119537179</v>
@@ -7165,31 +7165,31 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L38" t="n">
-        <v>950.0896384907273</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M38" t="n">
-        <v>1592.599638490728</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N38" t="n">
-        <v>2235.109638490728</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O38" t="n">
-        <v>2396.239739873683</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P38" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
       </c>
       <c r="R38" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S38" t="n">
         <v>2451.762030971221</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>492.6952769985969</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C39" t="n">
-        <v>452.1903149324157</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D39" t="n">
-        <v>424.9805301872615</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E39" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F39" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G39" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H39" t="n">
         <v>51.92</v>
@@ -7268,28 +7268,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R39" t="n">
-        <v>1886.686949702618</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S39" t="n">
-        <v>1753.535205884734</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T39" t="n">
-        <v>1671.337882527992</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U39" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V39" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X39" t="n">
-        <v>636.0770440818908</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y39" t="n">
-        <v>556.8938190655934</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="40">
@@ -7341,13 +7341,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,49 +7378,49 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D41" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H41" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I41" t="n">
         <v>51.92</v>
       </c>
       <c r="J41" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L41" t="n">
-        <v>949.6332762537361</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M41" t="n">
-        <v>1592.143276253736</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N41" t="n">
-        <v>1651.83297330616</v>
+        <v>1808.651587033441</v>
       </c>
       <c r="O41" t="n">
-        <v>1812.963074689115</v>
+        <v>1969.781688416396</v>
       </c>
       <c r="P41" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7429,25 +7429,25 @@
         <v>2596</v>
       </c>
       <c r="S41" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W41" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1316.525394051095</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C42" t="n">
-        <v>1276.020431984914</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D42" t="n">
-        <v>924.5682229973354</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E42" t="n">
-        <v>578.4347914600498</v>
+        <v>727.3319471348246</v>
       </c>
       <c r="F42" t="n">
-        <v>235.3678800076489</v>
+        <v>708.507459924848</v>
       </c>
       <c r="G42" t="n">
-        <v>231.3278685463101</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H42" t="n">
         <v>51.92</v>
@@ -7505,28 +7505,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>2062.032218270268</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S42" t="n">
-        <v>1928.880474452383</v>
+        <v>1753.535205884733</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095642</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U42" t="n">
-        <v>1766.721857646244</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V42" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W42" t="n">
-        <v>1559.768514109528</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X42" t="n">
-        <v>1459.907161134389</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y42" t="n">
-        <v>1380.723936118092</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="43">
@@ -7563,28 +7563,28 @@
         <v>1515.576154611867</v>
       </c>
       <c r="K43" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024221</v>
       </c>
       <c r="L43" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405832</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468664</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605562</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111773</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645972</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425882356</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949748849</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C44" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D44" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E44" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F44" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G44" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H44" t="n">
         <v>51.92</v>
@@ -7642,49 +7642,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L44" t="n">
-        <v>991.9887866314309</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M44" t="n">
-        <v>1595.767892278425</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N44" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O44" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P44" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S44" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W44" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X44" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>686.2820590119658</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C45" t="n">
-        <v>645.7770969457847</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D45" t="n">
-        <v>618.5673122006306</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E45" t="n">
-        <v>596.6763049057694</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F45" t="n">
-        <v>253.6093934533685</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G45" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H45" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I45" t="n">
         <v>51.92</v>
@@ -7748,22 +7748,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095641</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U45" t="n">
-        <v>1460.720946849539</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V45" t="n">
-        <v>1366.265727464165</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W45" t="n">
-        <v>1253.767603312823</v>
+        <v>735.9383970570296</v>
       </c>
       <c r="X45" t="n">
-        <v>829.6638260952597</v>
+        <v>636.0770440818907</v>
       </c>
       <c r="Y45" t="n">
-        <v>750.4806010789623</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="46">
@@ -7809,16 +7809,16 @@
         <v>1505.227982468588</v>
       </c>
       <c r="N46" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R46" t="n">
         <v>82.79157247680381</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>242.0199542155221</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>652.1121099729598</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>776.3653500296342</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>373.4816735941929</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>315.3213213472141</v>
       </c>
       <c r="Q2" t="n">
-        <v>501.1077446289929</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8049,7 +8049,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>384.3316744713784</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>299.5314174862185</v>
+        <v>183.5817792952637</v>
       </c>
       <c r="K5" t="n">
-        <v>321.3286984924623</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>308.6565929648241</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>471.5549969890509</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>777.3653500296342</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4816735941929551</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.1077446289929</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K8" t="n">
-        <v>246.8601159786807</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L8" t="n">
-        <v>308.6565929648241</v>
+        <v>309.2909949748743</v>
       </c>
       <c r="M8" t="n">
-        <v>845.554996989051</v>
+        <v>772.4711016975159</v>
       </c>
       <c r="N8" t="n">
-        <v>403.3653500296342</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
-        <v>374.4816735941929</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.1077446289929</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>560.3048366155554</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,16 +8915,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>473.0880804020101</v>
+        <v>3.200256351209731</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M14" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N14" t="n">
-        <v>248.0013330166451</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>950.4344291498551</v>
+        <v>481.0075770556116</v>
       </c>
       <c r="N17" t="n">
-        <v>840.3699380391354</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427137</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N20" t="n">
-        <v>452.3875733122749</v>
+        <v>376.7934807861708</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q20" t="n">
         <v>23.48346824708341</v>
@@ -9626,25 +9626,25 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>950.4344291498551</v>
+        <v>341.6095732017122</v>
       </c>
       <c r="N23" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9866,19 +9866,19 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L26" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>950.4344291498551</v>
+        <v>460.8900978221925</v>
       </c>
       <c r="N26" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q26" t="n">
         <v>23.48346824708341</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>179.5731479057567</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>230.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>950.4344291498551</v>
+        <v>792.031789021288</v>
       </c>
       <c r="N32" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>202.5956441962828</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,13 +10571,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M35" t="n">
         <v>950.4344291498551</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>27.14469655484982</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>560.3048366155554</v>
       </c>
       <c r="N38" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q38" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>290.7846768324985</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>433.9659648939236</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,13 +11285,13 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M44" t="n">
-        <v>911.3123136417682</v>
+        <v>361.2660804785743</v>
       </c>
       <c r="N44" t="n">
         <v>879.4920535472222</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.92739353920978</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23417,7 +23417,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23654,13 +23654,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8382458495976266</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24833,10 +24833,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -25082,7 +25082,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25307,7 +25307,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -25325,7 +25325,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495221599</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26024,7 +26024,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>954851.2427442853</v>
+        <v>955147.7830712959</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1836521.935436107</v>
+        <v>1836711.711304112</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2718085.863668924</v>
+        <v>2718275.639536929</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3599283.767871468</v>
+        <v>3599391.162239473</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4480833.613574012</v>
+        <v>4480941.007942016</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5362383.459276554</v>
+        <v>5362490.853644559</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6243933.304979094</v>
+        <v>6244040.699347098</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7125483.150681634</v>
+        <v>7125590.545049638</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8007032.996384173</v>
+        <v>8007140.390752177</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8888582.842086712</v>
+        <v>8888690.236454718</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9770132.687789259</v>
+        <v>9770240.082157264</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10651682.53349181</v>
+        <v>10651789.92785981</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11533232.37919436</v>
+        <v>11533339.77356236</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12414782.22489691</v>
+        <v>12414889.61926491</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13296332.07059946</v>
+        <v>13296439.46496746</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1322184.800797218</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="C2" t="n">
         <v>1322345.892349224</v>
@@ -26278,7 +26278,7 @@
         <v>1322345.892349224</v>
       </c>
       <c r="E2" t="n">
-        <v>1322324.768553815</v>
+        <v>1322324.768553814</v>
       </c>
       <c r="F2" t="n">
         <v>1322324.768553814</v>
@@ -26287,19 +26287,19 @@
         <v>1322324.768553814</v>
       </c>
       <c r="H2" t="n">
-        <v>1322324.768553815</v>
+        <v>1322324.768553814</v>
       </c>
       <c r="I2" t="n">
         <v>1322324.768553815</v>
       </c>
       <c r="J2" t="n">
+        <v>1322324.768553815</v>
+      </c>
+      <c r="K2" t="n">
         <v>1322324.768553814</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1322324.768553815</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1322324.768553814</v>
       </c>
       <c r="M2" t="n">
         <v>1322324.768553815</v>
@@ -26308,10 +26308,10 @@
         <v>1322324.768553815</v>
       </c>
       <c r="O2" t="n">
+        <v>1322324.768553817</v>
+      </c>
+      <c r="P2" t="n">
         <v>1322324.768553815</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1322324.768553814</v>
       </c>
     </row>
     <row r="3">
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231721</v>
+        <v>231098</v>
       </c>
       <c r="C3" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>588575</v>
+        <v>589550</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388096</v>
+        <v>388448</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577307.7597977305</v>
+        <v>570963.5697337883</v>
       </c>
       <c r="C4" t="n">
-        <v>575232.1895180241</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573221.1009892204</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562992</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308644</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286012</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301401</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58551.39999999999</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58612.2</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>58612.2</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>454604.640999487</v>
+        <v>461693.922615436</v>
       </c>
       <c r="C6" t="n">
-        <v>688149.5028312003</v>
+        <v>694800.8448029243</v>
       </c>
       <c r="D6" t="n">
-        <v>690512.5913600037</v>
+        <v>696812.4922187485</v>
       </c>
       <c r="E6" t="n">
-        <v>169866.2397576403</v>
+        <v>175354.2308879935</v>
       </c>
       <c r="F6" t="n">
-        <v>760127.3025758623</v>
+        <v>766590.2937062165</v>
       </c>
       <c r="G6" t="n">
-        <v>761815.6920975152</v>
+        <v>768278.6832278693</v>
       </c>
       <c r="H6" t="n">
-        <v>763506.4250074787</v>
+        <v>769969.416137832</v>
       </c>
       <c r="I6" t="n">
-        <v>765199.5182080257</v>
+        <v>771662.50933838</v>
       </c>
       <c r="J6" t="n">
-        <v>378798.9888229495</v>
+        <v>384909.9799533044</v>
       </c>
       <c r="K6" t="n">
-        <v>768240.8542017841</v>
+        <v>775055.8453321377</v>
       </c>
       <c r="L6" t="n">
-        <v>770293.1319241273</v>
+        <v>776756.1230544822</v>
       </c>
       <c r="M6" t="n">
-        <v>675195.8398040953</v>
+        <v>681658.8309344503</v>
       </c>
       <c r="N6" t="n">
-        <v>773700.9958948598</v>
+        <v>780163.9870252139</v>
       </c>
       <c r="O6" t="n">
-        <v>518608.6184933218</v>
+        <v>525071.6096236771</v>
       </c>
       <c r="P6" t="n">
-        <v>777118.7261449045</v>
+        <v>783581.717275259</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -26984,7 +26984,7 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -26993,7 +26993,7 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>321</v>
@@ -27002,7 +27002,7 @@
         <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>275</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27445,16 +27445,16 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>399.9999999999988</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.1177124465037</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>224.8682520946261</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27524,13 +27524,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0284079411381</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27566,16 +27566,16 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>31.46477465147608</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>27.19578428848864</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>315.4729657100833</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>239.121870533951</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27591,37 +27591,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>287.525971992607</v>
       </c>
       <c r="G4" t="n">
-        <v>244.858135136612</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1197490524383</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>171.047816275856</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>246.6329932583707</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,16 +27642,16 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2309599488807</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>132.1643059857123</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>224.8682520946261</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,13 +27764,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.517988705216</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0284079411381</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.7989632036872</v>
+        <v>13.06671792211793</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>139.2879192693876</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27828,37 +27828,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>294.3826718271959</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.858135136612</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.047816275856</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.13729309820286</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
-        <v>266.941429538848</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27888,16 +27888,16 @@
         <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>269.8873298096613</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>398.0465935392086</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I8" t="n">
-        <v>134.1177124465037</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>224.8682520946261</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27992,22 +27992,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>162.3093019948107</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>209.4985557026693</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,19 +28040,19 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>274.5727974528599</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28077,22 +28077,22 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.858135136612</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1197490524383</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I10" t="n">
-        <v>171.047816275856</v>
+        <v>290.0512875585939</v>
       </c>
       <c r="J10" t="n">
-        <v>22.13729309820286</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>311.007219975692</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,16 +28116,16 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28223,22 +28223,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
         <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>321</v>
@@ -28268,19 +28268,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>321</v>
@@ -28289,10 +28289,10 @@
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28460,16 +28460,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>321</v>
@@ -28505,19 +28505,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>321</v>
@@ -28636,10 +28636,10 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,13 +28697,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -28757,16 +28757,16 @@
         <v>321</v>
       </c>
       <c r="V18" t="n">
+        <v>321</v>
+      </c>
+      <c r="W18" t="n">
+        <v>321</v>
+      </c>
+      <c r="X18" t="n">
         <v>147.4081841180271</v>
       </c>
-      <c r="W18" t="n">
-        <v>321</v>
-      </c>
-      <c r="X18" t="n">
-        <v>321</v>
-      </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -28873,7 +28873,7 @@
         <v>321</v>
       </c>
       <c r="H20" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I20" t="n">
         <v>96.76634561233286</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>321</v>
@@ -28946,7 +28946,7 @@
         <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -29000,7 +29000,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -29171,16 +29171,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -29240,7 +29240,7 @@
         <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
     </row>
     <row r="25">
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29417,16 +29417,16 @@
         <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="I27" t="n">
         <v>191.6509141932353</v>
@@ -29456,13 +29456,13 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="U27" t="n">
         <v>321</v>
@@ -29578,7 +29578,7 @@
         <v>321</v>
       </c>
       <c r="F29" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G29" t="n">
         <v>321</v>
@@ -29617,7 +29617,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S29" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T29" t="n">
         <v>321</v>
@@ -29648,13 +29648,13 @@
         <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
         <v>321</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -29663,7 +29663,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>147.4081841180268</v>
+        <v>147.4081841180273</v>
       </c>
       <c r="I30" t="n">
         <v>191.6509141932353</v>
@@ -29815,7 +29815,7 @@
         <v>321</v>
       </c>
       <c r="F32" t="n">
-        <v>320.5394126346857</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="G32" t="n">
         <v>321</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>321</v>
@@ -29894,7 +29894,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29939,7 +29939,7 @@
         <v>321</v>
       </c>
       <c r="U33" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="V33" t="n">
         <v>321</v>
@@ -29951,7 +29951,7 @@
         <v>321</v>
       </c>
       <c r="Y33" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
     </row>
     <row r="34">
@@ -30061,7 +30061,7 @@
         <v>321</v>
       </c>
       <c r="I35" t="n">
-        <v>96.3057582470185</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30119,7 +30119,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C36" t="n">
         <v>321</v>
@@ -30128,10 +30128,10 @@
         <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
@@ -30173,22 +30173,22 @@
         <v>321</v>
       </c>
       <c r="T36" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="U36" t="n">
         <v>321</v>
       </c>
       <c r="V36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37">
@@ -30325,10 +30325,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S38" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T38" t="n">
         <v>321</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>321</v>
@@ -30368,7 +30368,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
@@ -30404,7 +30404,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="S39" t="n">
         <v>321</v>
@@ -30416,13 +30416,13 @@
         <v>321</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W39" t="n">
         <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="Y39" t="n">
         <v>321</v>
@@ -30535,7 +30535,7 @@
         <v>321</v>
       </c>
       <c r="I41" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30565,7 +30565,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S41" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T41" t="n">
         <v>321</v>
@@ -30599,19 +30599,19 @@
         <v>321</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>147.408184118027</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>191.6509141932353</v>
@@ -30641,7 +30641,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>321</v>
+        <v>147.4081841180265</v>
       </c>
       <c r="S42" t="n">
         <v>321</v>
@@ -30650,7 +30650,7 @@
         <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>321</v>
@@ -30699,7 +30699,7 @@
         <v>321</v>
       </c>
       <c r="K43" t="n">
-        <v>321</v>
+        <v>321.0000000000769</v>
       </c>
       <c r="L43" t="n">
         <v>321</v>
@@ -30769,7 +30769,7 @@
         <v>321</v>
       </c>
       <c r="H44" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I44" t="n">
         <v>96.76634561233286</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>321</v>
@@ -30842,7 +30842,7 @@
         <v>321</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
@@ -30851,7 +30851,7 @@
         <v>321</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30884,19 +30884,19 @@
         <v>321</v>
       </c>
       <c r="T45" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="U45" t="n">
-        <v>18.05909831126212</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>321</v>
       </c>
       <c r="W45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y45" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H2" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I2" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J2" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N2" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O2" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P2" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R2" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S2" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H3" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I3" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J3" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K3" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L3" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M3" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O3" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P3" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R3" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S3" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H4" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I4" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J4" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K4" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L4" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M4" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N4" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O4" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P4" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R4" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S4" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H5" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I5" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J5" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K5" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L5" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N5" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O5" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P5" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R5" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S5" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H6" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I6" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J6" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K6" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L6" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M6" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O6" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P6" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R6" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S6" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H7" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I7" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J7" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K7" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L7" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M7" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N7" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O7" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P7" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R7" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S7" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H8" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I8" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J8" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K8" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L8" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N8" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O8" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P8" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R8" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S8" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H9" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I9" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J9" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K9" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L9" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M9" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O9" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P9" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R9" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S9" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H10" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I10" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J10" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K10" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L10" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M10" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N10" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O10" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P10" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R10" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S10" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1006972724976123</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>294.1798838637633</v>
       </c>
       <c r="L2" t="n">
-        <v>65.3434070351759</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
-        <v>180.5571129839088</v>
+        <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P2" t="n">
-        <v>59.25677413017286</v>
+        <v>374</v>
       </c>
       <c r="Q2" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>146.1399552942795</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K3" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L3" t="n">
-        <v>318.4376284546069</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M3" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O3" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P3" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,22 +34877,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>13.14311602486508</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -34901,13 +34901,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>224.4957001601678</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4.06650298976183</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0517398730831</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34980,16 +34980,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>299.6321147587161</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="K5" t="n">
+        <v>52.15992964824122</v>
+      </c>
+      <c r="L5" t="n">
+        <v>64.70900502512563</v>
+      </c>
+      <c r="M5" t="n">
         <v>374</v>
-      </c>
-      <c r="L5" t="n">
-        <v>374</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>374</v>
@@ -34998,10 +34998,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>59.25677413017286</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>146.1399552942795</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K6" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L6" t="n">
-        <v>322.1952904430266</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M6" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O6" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P6" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,37 +35114,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>8.846453771640441</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.86342193648881</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7690400511193</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0517398730831</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>70.71701959344506</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35217,25 +35217,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1006972724976123</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>299.5314174862184</v>
+        <v>374</v>
       </c>
       <c r="L8" t="n">
+        <v>373.9999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>300.2102102361031</v>
+      </c>
+      <c r="N8" t="n">
         <v>374</v>
       </c>
-      <c r="M8" t="n">
-        <v>374</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>59.25677413017286</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>146.1399552942795</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K9" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L9" t="n">
-        <v>322.1952904430266</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M9" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O9" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P9" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35363,25 +35363,25 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>118.9492417745412</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>44.06579043684406</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L10" t="n">
-        <v>4.06650298976183</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,16 +35402,16 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L11" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M11" t="n">
-        <v>258.8704074657004</v>
+        <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P11" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35694,16 +35694,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
+        <v>179.1121759491997</v>
+      </c>
+      <c r="L14" t="n">
         <v>649</v>
-      </c>
-      <c r="L14" t="n">
-        <v>218.2342914572864</v>
       </c>
       <c r="M14" t="n">
         <v>649</v>
       </c>
       <c r="N14" t="n">
-        <v>17.50927946942293</v>
+        <v>649</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -35712,7 +35712,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>649</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L17" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M17" t="n">
+        <v>179.5731479057567</v>
+      </c>
+      <c r="N17" t="n">
         <v>649</v>
-      </c>
-      <c r="N17" t="n">
-        <v>609.8778844919133</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L20" t="n">
-        <v>649.0000000000001</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M20" t="n">
         <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>221.8955197650528</v>
+        <v>146.3014272389487</v>
       </c>
       <c r="O20" t="n">
-        <v>162.757678164601</v>
+        <v>649</v>
       </c>
       <c r="P20" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36317,7 +36317,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H22" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I22" t="n">
         <v>163.0214951995539</v>
@@ -36405,25 +36405,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K23" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L23" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M23" t="n">
+        <v>40.17514405185721</v>
+      </c>
+      <c r="N23" t="n">
         <v>649</v>
-      </c>
-      <c r="L23" t="n">
-        <v>649</v>
-      </c>
-      <c r="M23" t="n">
-        <v>649</v>
-      </c>
-      <c r="N23" t="n">
-        <v>179.1121759491994</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36645,19 +36645,19 @@
         <v>649</v>
       </c>
       <c r="L26" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M26" t="n">
+        <v>159.4556686723375</v>
+      </c>
+      <c r="N26" t="n">
         <v>649</v>
-      </c>
-      <c r="M26" t="n">
-        <v>649</v>
-      </c>
-      <c r="N26" t="n">
-        <v>179.1121759491994</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P26" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L29" t="n">
-        <v>397.8074393630432</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
         <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -36897,7 +36897,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37116,16 +37116,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K32" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L32" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M32" t="n">
+        <v>490.597359871433</v>
+      </c>
+      <c r="N32" t="n">
         <v>649</v>
-      </c>
-      <c r="L32" t="n">
-        <v>649</v>
-      </c>
-      <c r="M32" t="n">
-        <v>649</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>179.1121759491994</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H34" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I34" t="n">
         <v>163.0214951995539</v>
@@ -37350,13 +37350,13 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L35" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M35" t="n">
         <v>649</v>
@@ -37371,7 +37371,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.661228307766413</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37502,7 +37502,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
-        <v>649</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="N38" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P38" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37739,7 +37739,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H40" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I40" t="n">
         <v>163.0214951995539</v>
@@ -37824,7 +37824,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
         <v>175.9119195979899</v>
@@ -37836,16 +37836,16 @@
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>60.29262328527629</v>
+        <v>649</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P41" t="n">
-        <v>198.5777841804241</v>
+        <v>632.5437490743477</v>
       </c>
       <c r="Q41" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37985,7 +37985,7 @@
         <v>329.5882314919611</v>
       </c>
       <c r="K43" t="n">
-        <v>104.5500458709881</v>
+        <v>104.550045871065</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38064,13 +38064,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L44" t="n">
         <v>649</v>
       </c>
-      <c r="L44" t="n">
-        <v>218.2342914572864</v>
-      </c>
       <c r="M44" t="n">
-        <v>609.8778844919133</v>
+        <v>59.83165132871935</v>
       </c>
       <c r="N44" t="n">
         <v>649</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
